--- a/artfynd/A 1724-2019 artfynd.xlsx
+++ b/artfynd/A 1724-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,339 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>115008663</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Högholmen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>400327</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6394744</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tvärred</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Överflygande med lockrop</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115008585</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högholmen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>400460</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6394751</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tvärred</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115008661</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56695</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högholmen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>400318</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6394724</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tvärred</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spelflykt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
